--- a/data/trans_dic/P45C_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,9</t>
+          <t>0,46; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,96</t>
+          <t>0,59; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,91</t>
+          <t>0,37; 1,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,1</t>
+          <t>1,24; 3,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,7</t>
+          <t>0,62; 1,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,32</t>
+          <t>0,92; 2,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,62</t>
+          <t>0,39; 1,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,87</t>
+          <t>0,65; 1,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,52</t>
+          <t>0,68; 1,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,9</t>
+          <t>0,92; 1,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,48</t>
+          <t>0,5; 1,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,41</t>
+          <t>1,06; 2,33</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,97</t>
+          <t>1,45; 3,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,07</t>
+          <t>0,93; 2,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,46</t>
+          <t>0,54; 1,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,19</t>
+          <t>0,88; 2,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,86</t>
+          <t>1,34; 2,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,25</t>
+          <t>0,98; 2,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,84</t>
+          <t>0,77; 1,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,94</t>
+          <t>0,88; 2,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,65</t>
+          <t>1,6; 2,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,93</t>
+          <t>1,09; 1,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,43</t>
+          <t>0,77; 1,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,85</t>
+          <t>1,0; 1,84</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,56</t>
+          <t>0,86; 3,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,48</t>
+          <t>0,41; 2,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,65</t>
+          <t>0,98; 3,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,8</t>
+          <t>1,05; 3,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,35</t>
+          <t>1,13; 4,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,34</t>
+          <t>0,41; 2,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,16</t>
+          <t>1,11; 3,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,16</t>
+          <t>1,14; 3,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,89</t>
+          <t>1,01; 2,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,8</t>
+          <t>0,5; 1,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,02</t>
+          <t>1,21; 2,86</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,26; 2,19</t>
+          <t>1,28; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,71</t>
+          <t>0,91; 1,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,32</t>
+          <t>0,62; 1,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,2</t>
+          <t>1,16; 2,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,13</t>
+          <t>1,28; 2,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,07</t>
+          <t>1,21; 2,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,5</t>
+          <t>0,77; 1,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,86</t>
+          <t>1,07; 1,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,05</t>
+          <t>1,37; 2,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,77</t>
+          <t>1,18; 1,75</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,28</t>
+          <t>0,77; 1,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,83</t>
+          <t>1,2; 1,93</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas</t>
+          <t>Población que han sufrido a lo largo de este ultimo año alguna quemadura solar con ampollas (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5474; 19522</t>
+          <t>4771; 18066</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4987; 18988</t>
+          <t>5685; 19580</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2912; 14264</t>
+          <t>2750; 14140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6204; 21076</t>
+          <t>6373; 20248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7518; 22333</t>
+          <t>8095; 23195</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11584; 30618</t>
+          <t>12117; 30099</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3651; 15918</t>
+          <t>3794; 15541</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4928; 14104</t>
+          <t>4935; 14273</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15398; 35599</t>
+          <t>15847; 35784</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19982; 43503</t>
+          <t>20964; 44362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9437; 25648</t>
+          <t>8572; 23856</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13130; 30627</t>
+          <t>13405; 29523</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24223; 50135</t>
+          <t>24552; 50828</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18648; 40446</t>
+          <t>18112; 39236</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11702; 30118</t>
+          <t>11231; 29992</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19057; 49938</t>
+          <t>20089; 49448</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21828; 45310</t>
+          <t>21196; 44399</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16848; 39166</t>
+          <t>17088; 37797</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15535; 36364</t>
+          <t>15268; 35430</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19421; 43385</t>
+          <t>19569; 44701</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52053; 86800</t>
+          <t>52228; 85940</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41336; 71408</t>
+          <t>40406; 68349</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31641; 57556</t>
+          <t>30914; 58575</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45348; 83815</t>
+          <t>45048; 83353</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4577; 19575</t>
+          <t>4750; 18848</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2055; 11798</t>
+          <t>1955; 12118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>978; 12652</t>
+          <t>968; 12657</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5280; 23576</t>
+          <t>6319; 25332</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4930; 18085</t>
+          <t>4991; 18821</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5233; 19828</t>
+          <t>5139; 18868</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2018; 12701</t>
+          <t>2201; 11973</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7218; 20845</t>
+          <t>7340; 21954</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12283; 32463</t>
+          <t>11706; 31724</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9396; 26943</t>
+          <t>9403; 25705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4905; 19493</t>
+          <t>5409; 19180</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16002; 39507</t>
+          <t>15773; 37369</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41158; 71594</t>
+          <t>41915; 72746</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32127; 58062</t>
+          <t>30927; 58015</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20421; 44350</t>
+          <t>20839; 44659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39158; 75917</t>
+          <t>39939; 76061</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42023; 71951</t>
+          <t>43297; 73097</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42943; 72738</t>
+          <t>42496; 72486</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27428; 52662</t>
+          <t>27018; 51942</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38469; 67970</t>
+          <t>38939; 68003</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>92764; 135990</t>
+          <t>91197; 133070</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81717; 122358</t>
+          <t>81627; 120863</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55475; 87740</t>
+          <t>52797; 87391</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84320; 130206</t>
+          <t>85157; 137168</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R1-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R1-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,76</t>
+          <t>0,47; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,03</t>
+          <t>0,6; 2,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,89</t>
+          <t>0,39; 1,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,94</t>
+          <t>1,17; 3,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,77</t>
+          <t>0,6; 1,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,28</t>
+          <t>0,91; 2,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,58</t>
+          <t>0,4; 1,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,89</t>
+          <t>0,66; 1,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,53</t>
+          <t>0,66; 1,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,94</t>
+          <t>0,89; 1,83</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,38</t>
+          <t>0,52; 1,47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,33</t>
+          <t>0,98; 2,21</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,01</t>
+          <t>1,46; 2,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,01</t>
+          <t>0,96; 2,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 1,46</t>
+          <t>0,57; 1,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,16</t>
+          <t>1,05; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,81</t>
+          <t>1,39; 2,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,17</t>
+          <t>0,99; 2,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,79</t>
+          <t>0,8; 1,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,0</t>
+          <t>1,08; 2,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,63</t>
+          <t>1,64; 2,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,09; 1,85</t>
+          <t>1,11; 1,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,45</t>
+          <t>0,78; 1,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,84</t>
+          <t>1,16; 2,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,42</t>
+          <t>0,8; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,55</t>
+          <t>0,44; 2,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,34</t>
+          <t>0,18; 2,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,92</t>
+          <t>0,94; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,96</t>
+          <t>1,04; 3,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,14</t>
+          <t>1,13; 4,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,21</t>
+          <t>0,37; 2,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,32</t>
+          <t>1,24; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,09</t>
+          <t>1,14; 2,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,76</t>
+          <t>1,01; 2,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,77</t>
+          <t>0,46; 1,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,86</t>
+          <t>1,26; 2,97</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,23</t>
+          <t>1,27; 2,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,71</t>
+          <t>0,92; 1,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,33</t>
+          <t>0,6; 1,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,21</t>
+          <t>1,29; 2,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,17</t>
+          <t>1,26; 2,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,06</t>
+          <t>1,22; 2,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,48</t>
+          <t>0,79; 1,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,86</t>
+          <t>1,22; 1,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,75</t>
+          <t>1,16; 1,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,27</t>
+          <t>0,78; 1,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,93</t>
+          <t>1,34; 1,97</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>21201</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4771; 18066</t>
+          <t>4798; 18091</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5685; 19580</t>
+          <t>5754; 19335</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2750; 14140</t>
+          <t>2935; 13737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6373; 20248</t>
+          <t>6746; 20980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8095; 23195</t>
+          <t>7826; 22884</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12117; 30099</t>
+          <t>12019; 29614</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3794; 15541</t>
+          <t>3964; 15722</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4935; 14273</t>
+          <t>5408; 14529</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15847; 35784</t>
+          <t>15469; 34474</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20964; 44362</t>
+          <t>20464; 41903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8572; 23856</t>
+          <t>9053; 25412</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13405; 29523</t>
+          <t>13746; 30856</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62273</t>
+          <t>67607</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24552; 50828</t>
+          <t>24664; 49062</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18112; 39236</t>
+          <t>18715; 40663</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11231; 29992</t>
+          <t>11756; 30506</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20089; 49448</t>
+          <t>23379; 50528</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21196; 44399</t>
+          <t>21949; 44735</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17088; 37797</t>
+          <t>17282; 37521</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15268; 35430</t>
+          <t>15731; 35930</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19569; 44701</t>
+          <t>23310; 46165</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52228; 85940</t>
+          <t>53599; 86186</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40406; 68349</t>
+          <t>40871; 69876</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30914; 58575</t>
+          <t>31671; 57961</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45048; 83353</t>
+          <t>51102; 87927</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>28824</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4750; 18848</t>
+          <t>4396; 19023</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1955; 12118</t>
+          <t>2087; 12005</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>968; 12657</t>
+          <t>967; 12783</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6319; 25332</t>
+          <t>6676; 26379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4991; 18821</t>
+          <t>4952; 18326</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5139; 18868</t>
+          <t>5158; 19450</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2201; 11973</t>
+          <t>2028; 11769</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7340; 21954</t>
+          <t>9092; 24942</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11706; 31724</t>
+          <t>11695; 30350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9403; 25705</t>
+          <t>9392; 26051</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5409; 19180</t>
+          <t>5034; 20019</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15773; 37369</t>
+          <t>18202; 42958</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41915; 72746</t>
+          <t>41443; 72470</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30927; 58015</t>
+          <t>31167; 58731</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20839; 44659</t>
+          <t>20112; 43524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39939; 76061</t>
+          <t>45309; 79984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43297; 73097</t>
+          <t>42484; 72232</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42496; 72486</t>
+          <t>42861; 74166</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27018; 51942</t>
+          <t>27692; 55014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>38939; 68003</t>
+          <t>45367; 74276</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91197; 133070</t>
+          <t>92113; 136039</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81627; 120863</t>
+          <t>80241; 124677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52797; 87391</t>
+          <t>53766; 87398</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85157; 137168</t>
+          <t>97270; 142701</t>
         </is>
       </c>
     </row>
